--- a/outputs/resultats/bnc/2025_t3_vs_2025_t2/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t3_vs_2025_t2/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,9 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,6 +514,21 @@
           <t>Commentaire analyste</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut validation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validé par</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Validé le</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -556,9 +574,24 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T20:27:45.126530+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2025_t3_vs_2025_t2/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t3_vs_2025_t2/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -451,11 +451,10 @@
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,12 +470,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Page T1</t>
+          <t>Page (trimestre précédent)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Page T2</t>
+          <t>Page (trimestre courant)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -491,12 +490,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Libellé T1</t>
+          <t>Libellé (trimestre précédent)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Libellé T2</t>
+          <t>Libellé (trimestre courant)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -506,7 +505,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Nouvelle divulgation ?</t>
+          <t>Nouvelle idée ?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -520,11 +519,6 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Validé par</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Validé le</t>
         </is>
@@ -533,65 +527,154 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>s.o. Sans objet</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>La note de bas de page marquée par un astérisque, indiquant 's.o. Sans objet', a été retirée du tableau des exigences de déclaration du ratio de liquidité à court terme au T3 2025. Cette note était présente dans le rapport précédent du rapport courant 2025. L'impact de la suppression de cette note est principalement cosmétique, car elle indiquait simplement que certaines informations n'étaient pas applicables. Cela n'affecte pas directement les calculs ou les divulgations réglementaires, mais peut influencer la clarté de la présentation des données pour les utilisateurs du rapport. Il s'agit d'une mise à jour ordinaire qui n'a pas de conséquences significatives sur la conformité réglementaire ou la méthodologie de calcul. L'analyste peut confirmer cette suppression comme une simplification de la présentation sans nécessiter d'analyse approfondie supplémentaire.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>s.o. Sans objet</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>La note de bas de page 's.o. Sans objet' a été retirée du tableau des exigences réglementaires des ratios de fonds propres, de levier et TLAC. Cette note indiquait simplement qu'une certaine information était sans objet, ce qui est souvent utilisé pour clarifier l'absence de données ou de pertinence pour un élément spécifique du tableau. L'impact de la suppression de cette note est principalement cosmétique, car elle ne modifie pas les informations financières ou réglementaires présentées dans le tableau. Elle n'affecte pas non plus les calculs des ratios ou les exigences de divulgation selon les normes de Bâle III ou les directives du BSIF. Par conséquent, cette suppression n'a pas de conséquences réglementaires ou méthodologiques directes. Il s'agit d'une mise à jour ordinaire visant probablement à simplifier la présentation du tableau. L'analyste peut confirmer que cette suppression n'entraîne pas de confusion ou de malentendu pour les utilisateurs du rapport, mais aucune action supplémentaire n'est nécessaire.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Tableau</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Nouveau tableau détecté dans le trimestre courant.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-18T20:27:45.126530+00:00</t>
-        </is>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:M4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>